--- a/Libraries/Vehicle/Steer/Ackermann/sm_car_data_Steer_Ackermann.xlsx
+++ b/Libraries/Vehicle/Steer/Ackermann/sm_car_data_Steer_Ackermann.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\vtpVDG\Libraries\Vehicle\Steer\Ackermann\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Steer\Ackermann\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94447006-C908-468F-BB52-804CDDC4D57B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FD9791D-E16D-4D08-AB59-C505FEA592E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3525" yWindow="1125" windowWidth="21600" windowHeight="11235" tabRatio="717" activeTab="4" xr2:uid="{6551A3D7-48D1-475C-90BB-3A0F5E8315B3}"/>
+    <workbookView xWindow="31050" yWindow="0" windowWidth="23535" windowHeight="15585" tabRatio="817" activeTab="7" xr2:uid="{6551A3D7-48D1-475C-90BB-3A0F5E8315B3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sedan_Hamba_f" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="40">
   <si>
     <t>Units</t>
   </si>
@@ -145,6 +145,21 @@
   </si>
   <si>
     <t>Ackermann_Landy_f</t>
+  </si>
+  <si>
+    <t>aKPI</t>
+  </si>
+  <si>
+    <t>deg</t>
+  </si>
+  <si>
+    <t>Positive KPI: Top Inside Bottom</t>
+  </si>
+  <si>
+    <t>aCaster</t>
+  </si>
+  <si>
+    <t>Positive Caster: Top Rear of WC</t>
   </si>
 </sst>
 </file>
@@ -783,7 +798,7 @@
   <sheetPr>
     <tabColor rgb="FFFF9999"/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="11" customWidth="1"/>
@@ -866,133 +881,155 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>12</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B6" s="5"/>
       <c r="C6" s="5"/>
       <c r="D6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="13">
-        <v>-1.0213531220517</v>
-      </c>
-      <c r="G6" s="13">
-        <v>0.37675517503754502</v>
-      </c>
-      <c r="H6" s="13">
-        <v>0.92326153885340301</v>
+        <v>36</v>
+      </c>
+      <c r="E6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-      <c r="B7" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="A7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13">
-        <v>0.35289999999999999</v>
+        <v>36</v>
+      </c>
+      <c r="E7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
+      <c r="A8" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="B8" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
+        <v>13</v>
+      </c>
+      <c r="F8" s="13">
+        <v>-1.0213531220517</v>
+      </c>
+      <c r="G8" s="13">
+        <v>0.37675517503754502</v>
+      </c>
       <c r="H8" s="13">
-        <v>1</v>
+        <v>0.92326153885340301</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="5" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C9" s="5"/>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
       <c r="F9" s="13"/>
       <c r="G9" s="13"/>
-      <c r="H9" s="14" t="s">
-        <v>32</v>
+      <c r="H9" s="13">
+        <v>0.35289999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>20</v>
-      </c>
+      <c r="A10" s="4"/>
       <c r="B10" s="5" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" t="s">
-        <v>19</v>
+        <v>16</v>
+      </c>
+      <c r="E10" t="s">
+        <v>17</v>
       </c>
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
       <c r="H10" s="13">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="5"/>
+      <c r="A11" s="4"/>
+      <c r="B11" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="C11" s="5"/>
-      <c r="D11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" t="s">
-        <v>31</v>
-      </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6">
-        <v>2.8239999999999998</v>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="14" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="5"/>
+        <v>20</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="C12" s="5"/>
       <c r="D12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" t="s">
         <v>13</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E13" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6">
+        <v>2.8239999999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6">
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6">
         <f>0.7865*2</f>
         <v>1.573</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F15" s="6"/>
@@ -1000,52 +1037,62 @@
       <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="11"/>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="11"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="11"/>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="11"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="11"/>
-      <c r="H20" s="12"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="11"/>
-      <c r="H21" s="12"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="11"/>
+      <c r="H22" s="12"/>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="11"/>
+      <c r="H23" s="12"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A20:A21">
+  <conditionalFormatting sqref="A22:A23">
     <cfRule type="cellIs" dxfId="31" priority="10" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:B4 A16:B19">
+  <conditionalFormatting sqref="A4:B4 A18:B21">
     <cfRule type="cellIs" dxfId="30" priority="12" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A6:B10">
+  <conditionalFormatting sqref="A8:B12">
     <cfRule type="cellIs" dxfId="29" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E6:E10">
+  <conditionalFormatting sqref="E8:E12">
     <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
@@ -1059,7 +1106,7 @@
   <sheetPr>
     <tabColor rgb="FFFF9999"/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="11" customWidth="1"/>
@@ -1142,67 +1189,89 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>18</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B6" s="5"/>
       <c r="C6" s="5"/>
       <c r="D6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13">
-        <v>100</v>
+        <v>36</v>
+      </c>
+      <c r="E6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6">
-        <v>2.8239999999999998</v>
+        <v>39</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="5"/>
+        <v>20</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="C8" s="5"/>
       <c r="D8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" t="s">
         <v>13</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6">
+        <v>2.8239999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6">
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6">
         <f>0.7865*2</f>
         <v>1.573</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F11" s="6"/>
@@ -1210,52 +1279,62 @@
       <c r="H11" s="6"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B12" s="11"/>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B13" s="11"/>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B14" s="11"/>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="11"/>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="11"/>
-      <c r="H16" s="12"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="11"/>
-      <c r="H17" s="12"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="11"/>
+      <c r="H18" s="12"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="11"/>
+      <c r="H19" s="12"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A16:A17">
+  <conditionalFormatting sqref="A18:A19">
     <cfRule type="cellIs" dxfId="27" priority="8" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:B4 A12:B15">
+  <conditionalFormatting sqref="A4:B4 A14:B17">
     <cfRule type="cellIs" dxfId="26" priority="10" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A6:B6">
+  <conditionalFormatting sqref="A8:B8">
     <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
+  <conditionalFormatting sqref="E8">
     <cfRule type="cellIs" dxfId="24" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
@@ -1269,7 +1348,7 @@
   <sheetPr>
     <tabColor rgb="FFFF9999"/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="11" customWidth="1"/>
@@ -1352,133 +1431,155 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>12</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B6" s="5"/>
       <c r="C6" s="5"/>
       <c r="D6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="6">
-        <v>-1.3243331220516996</v>
-      </c>
-      <c r="G6" s="6">
-        <v>0.45175517503754498</v>
-      </c>
-      <c r="H6" s="6">
-        <v>0.88921153885340298</v>
+        <v>36</v>
+      </c>
+      <c r="E6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-      <c r="B7" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="A7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13">
-        <v>0.35289999999999999</v>
+        <v>36</v>
+      </c>
+      <c r="E7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
+      <c r="A8" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="B8" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="F8" s="6">
+        <v>-1.3243331220516996</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0.45175517503754498</v>
+      </c>
+      <c r="H8" s="6">
+        <v>0.88921153885340298</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="5" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C9" s="5"/>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
       <c r="F9" s="13"/>
       <c r="G9" s="13"/>
-      <c r="H9" s="14" t="s">
-        <v>32</v>
+      <c r="H9" s="13">
+        <v>0.35289999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>20</v>
-      </c>
+      <c r="A10" s="4"/>
       <c r="B10" s="5" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" t="s">
-        <v>19</v>
+        <v>16</v>
+      </c>
+      <c r="E10" t="s">
+        <v>17</v>
       </c>
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
       <c r="H10" s="13">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="5"/>
+      <c r="A11" s="4"/>
+      <c r="B11" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="C11" s="5"/>
-      <c r="D11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" t="s">
-        <v>31</v>
-      </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6">
-        <v>3.57</v>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="14" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="5"/>
+        <v>20</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="C12" s="5"/>
       <c r="D12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" t="s">
         <v>13</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E13" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6">
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6">
         <f>0.9921*2</f>
         <v>1.9842</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F15" s="6"/>
@@ -1486,52 +1587,62 @@
       <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="11"/>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="11"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="11"/>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="11"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="11"/>
-      <c r="H20" s="12"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="11"/>
-      <c r="H21" s="12"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="11"/>
+      <c r="H22" s="12"/>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="11"/>
+      <c r="H23" s="12"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A20:A21">
+  <conditionalFormatting sqref="A22:A23">
     <cfRule type="cellIs" dxfId="23" priority="10" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:B4 A16:B19">
+  <conditionalFormatting sqref="A4:B4 A18:B21">
     <cfRule type="cellIs" dxfId="22" priority="12" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A6:B10">
+  <conditionalFormatting sqref="A8:B12">
     <cfRule type="cellIs" dxfId="21" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E6:E10">
+  <conditionalFormatting sqref="E8:E12">
     <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
@@ -1545,7 +1656,7 @@
   <sheetPr>
     <tabColor rgb="FFFF9999"/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="11" customWidth="1"/>
@@ -1628,67 +1739,89 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>18</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B6" s="5"/>
       <c r="C6" s="5"/>
       <c r="D6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13">
-        <v>100</v>
+        <v>36</v>
+      </c>
+      <c r="E6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6">
-        <v>3.57</v>
+        <v>39</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="5"/>
+        <v>20</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="C8" s="5"/>
       <c r="D8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" t="s">
         <v>13</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6">
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6">
         <f>0.9921*2</f>
         <v>1.9842</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F11" s="6"/>
@@ -1696,52 +1829,62 @@
       <c r="H11" s="6"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B12" s="11"/>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B13" s="11"/>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B14" s="11"/>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="11"/>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="11"/>
-      <c r="H16" s="12"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="11"/>
-      <c r="H17" s="12"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="11"/>
+      <c r="H18" s="12"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="11"/>
+      <c r="H19" s="12"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A16:A17">
+  <conditionalFormatting sqref="A18:A19">
     <cfRule type="cellIs" dxfId="19" priority="8" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:B4 A12:B15">
+  <conditionalFormatting sqref="A4:B4 A14:B17">
     <cfRule type="cellIs" dxfId="18" priority="10" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A6:B6">
+  <conditionalFormatting sqref="A8:B8">
     <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
+  <conditionalFormatting sqref="E8">
     <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
@@ -1755,7 +1898,7 @@
   <sheetPr>
     <tabColor rgb="FFFF9999"/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="11" customWidth="1"/>
@@ -1838,132 +1981,154 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>12</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B6" s="5"/>
       <c r="C6" s="5"/>
       <c r="D6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="13">
-        <v>-1.0213531220517</v>
-      </c>
-      <c r="G6" s="13">
-        <v>-0.37675517503754502</v>
-      </c>
-      <c r="H6" s="13">
-        <v>1.2232615388534001</v>
+        <v>36</v>
+      </c>
+      <c r="E6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-      <c r="B7" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="A7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13">
-        <v>0.35289999999999999</v>
+        <v>36</v>
+      </c>
+      <c r="E7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
+      <c r="A8" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="B8" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
+        <v>13</v>
+      </c>
+      <c r="F8" s="13">
+        <v>-1.0213531220517</v>
+      </c>
+      <c r="G8" s="13">
+        <v>-0.37675517503754502</v>
+      </c>
       <c r="H8" s="13">
-        <v>1</v>
+        <v>1.2232615388534001</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="5" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C9" s="5"/>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
       <c r="F9" s="13"/>
       <c r="G9" s="13"/>
-      <c r="H9" s="14" t="s">
-        <v>32</v>
+      <c r="H9" s="13">
+        <v>0.35289999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>20</v>
-      </c>
+      <c r="A10" s="4"/>
       <c r="B10" s="5" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" t="s">
-        <v>19</v>
+        <v>16</v>
+      </c>
+      <c r="E10" t="s">
+        <v>17</v>
       </c>
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
       <c r="H10" s="13">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="5"/>
+      <c r="A11" s="4"/>
+      <c r="B11" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="C11" s="5"/>
-      <c r="D11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" t="s">
-        <v>31</v>
-      </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6">
-        <v>2.82</v>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="14" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="5"/>
+        <v>20</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="C12" s="5"/>
       <c r="D12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" t="s">
         <v>13</v>
       </c>
-      <c r="E12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6">
-        <v>1.4859</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E13" t="s">
+        <v>31</v>
+      </c>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
+      <c r="H13" s="6">
+        <v>2.82</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" t="s">
+        <v>30</v>
+      </c>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
+      <c r="H14" s="6">
+        <v>1.4859</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F15" s="6"/>
@@ -1971,52 +2136,62 @@
       <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="11"/>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="11"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="11"/>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="11"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="11"/>
-      <c r="H20" s="12"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="11"/>
-      <c r="H21" s="12"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="11"/>
+      <c r="H22" s="12"/>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="11"/>
+      <c r="H23" s="12"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A20:A21">
+  <conditionalFormatting sqref="A22:A23">
     <cfRule type="cellIs" dxfId="15" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:B4 A16:B19">
+  <conditionalFormatting sqref="A4:B4 A18:B21">
     <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A6:B10">
+  <conditionalFormatting sqref="A8:B12">
     <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E6:E10">
+  <conditionalFormatting sqref="E8:E12">
     <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
@@ -2030,7 +2205,7 @@
   <sheetPr>
     <tabColor rgb="FFFF9999"/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="11" customWidth="1"/>
@@ -2113,133 +2288,155 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>12</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B6" s="5"/>
       <c r="C6" s="5"/>
       <c r="D6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="13">
-        <v>1.18</v>
-      </c>
-      <c r="G6" s="13">
-        <v>0.55926517503754503</v>
-      </c>
-      <c r="H6" s="13">
-        <v>1.34</v>
+        <v>36</v>
+      </c>
+      <c r="E6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-      <c r="B7" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="A7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13">
-        <v>0.78888879999999995</v>
+        <v>36</v>
+      </c>
+      <c r="E7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
+      <c r="A8" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="B8" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
+        <v>13</v>
+      </c>
+      <c r="F8" s="13">
+        <v>1.18</v>
+      </c>
+      <c r="G8" s="13">
+        <v>0.55926517503754503</v>
+      </c>
       <c r="H8" s="13">
-        <v>1</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="5" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C9" s="5"/>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
       <c r="F9" s="13"/>
       <c r="G9" s="13"/>
-      <c r="H9" s="14" t="s">
-        <v>32</v>
+      <c r="H9" s="13">
+        <v>0.78888879999999995</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>20</v>
-      </c>
+      <c r="A10" s="4"/>
       <c r="B10" s="5" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" t="s">
-        <v>19</v>
+        <v>16</v>
+      </c>
+      <c r="E10" t="s">
+        <v>17</v>
       </c>
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
       <c r="H10" s="13">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="5"/>
+      <c r="A11" s="4"/>
+      <c r="B11" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="C11" s="5"/>
-      <c r="D11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" t="s">
-        <v>31</v>
-      </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6">
-        <v>6.7816159999999996</v>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="14" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="5"/>
+        <v>20</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="C12" s="5"/>
       <c r="D12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" t="s">
         <v>13</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E13" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6">
+        <v>6.7816159999999996</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6">
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6">
         <f>0.83834*2</f>
         <v>1.6766799999999999</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F15" s="6"/>
@@ -2247,52 +2444,62 @@
       <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="11"/>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="11"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="11"/>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="11"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="11"/>
-      <c r="H20" s="12"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="11"/>
-      <c r="H21" s="12"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="11"/>
+      <c r="H22" s="12"/>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="11"/>
+      <c r="H23" s="12"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A20:A21">
+  <conditionalFormatting sqref="A22:A23">
     <cfRule type="cellIs" dxfId="11" priority="10" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:B4 A16:B19">
+  <conditionalFormatting sqref="A4:B4 A18:B21">
     <cfRule type="cellIs" dxfId="10" priority="12" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A6:B10">
+  <conditionalFormatting sqref="A8:B12">
     <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E6:E10">
+  <conditionalFormatting sqref="E8:E12">
     <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
@@ -2306,7 +2513,7 @@
   <sheetPr>
     <tabColor rgb="FFFF9999"/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="11" customWidth="1"/>
@@ -2389,133 +2596,155 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>12</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B6" s="5"/>
       <c r="C6" s="5"/>
       <c r="D6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="13">
-        <v>-0.97309999999999997</v>
-      </c>
-      <c r="G6" s="13">
-        <v>0.55801000000000001</v>
-      </c>
-      <c r="H6" s="13">
-        <v>2.5924</v>
+        <v>36</v>
+      </c>
+      <c r="E6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-      <c r="B7" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="A7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13">
-        <v>0.78888879999999995</v>
+        <v>36</v>
+      </c>
+      <c r="E7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
+      <c r="A8" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="B8" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
+        <v>13</v>
+      </c>
+      <c r="F8" s="13">
+        <v>-0.97309999999999997</v>
+      </c>
+      <c r="G8" s="13">
+        <v>0.55801000000000001</v>
+      </c>
       <c r="H8" s="13">
-        <v>1</v>
+        <v>2.5924</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="5" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C9" s="5"/>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
       <c r="F9" s="13"/>
       <c r="G9" s="13"/>
-      <c r="H9" s="14" t="s">
-        <v>32</v>
+      <c r="H9" s="13">
+        <v>0.78888879999999995</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>20</v>
-      </c>
+      <c r="A10" s="4"/>
       <c r="B10" s="5" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" t="s">
-        <v>19</v>
+        <v>16</v>
+      </c>
+      <c r="E10" t="s">
+        <v>17</v>
       </c>
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
       <c r="H10" s="13">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="5"/>
+      <c r="A11" s="4"/>
+      <c r="B11" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="C11" s="5"/>
-      <c r="D11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" t="s">
-        <v>31</v>
-      </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6">
-        <v>6.4820000000000002</v>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="14" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="5"/>
+        <v>20</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="C12" s="5"/>
       <c r="D12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" t="s">
         <v>13</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E13" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6">
+        <v>6.4820000000000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6">
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6">
         <f>0.96035*2</f>
         <v>1.9207000000000001</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F15" s="6"/>
@@ -2523,52 +2752,62 @@
       <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="11"/>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="11"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="11"/>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="11"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="11"/>
-      <c r="H20" s="12"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="11"/>
-      <c r="H21" s="12"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="11"/>
+      <c r="H22" s="12"/>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="11"/>
+      <c r="H23" s="12"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A20:A21">
+  <conditionalFormatting sqref="A22:A23">
     <cfRule type="cellIs" dxfId="7" priority="11" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:B4 A16:B19">
+  <conditionalFormatting sqref="A4:B4 A18:B21">
     <cfRule type="cellIs" dxfId="6" priority="13" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A6:B10">
+  <conditionalFormatting sqref="A8:B12">
     <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E6:E10">
+  <conditionalFormatting sqref="E8:E12">
     <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
@@ -2582,7 +2821,7 @@
   <sheetPr>
     <tabColor rgb="FFFF9999"/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="11" customWidth="1"/>
@@ -2665,133 +2904,155 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>12</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B6" s="5"/>
       <c r="C6" s="5"/>
       <c r="D6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="13">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="G6" s="13">
-        <v>0.60799999999999998</v>
-      </c>
-      <c r="H6" s="13">
-        <v>1.94</v>
+        <v>36</v>
+      </c>
+      <c r="E6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-      <c r="B7" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="A7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13">
-        <v>0.78888879999999995</v>
+        <v>36</v>
+      </c>
+      <c r="E7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
+      <c r="A8" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="B8" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
+        <v>13</v>
+      </c>
+      <c r="F8" s="13">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="G8" s="13">
+        <v>0.60799999999999998</v>
+      </c>
       <c r="H8" s="13">
-        <v>1</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="5" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C9" s="5"/>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
       <c r="F9" s="13"/>
       <c r="G9" s="13"/>
-      <c r="H9" s="14" t="s">
-        <v>32</v>
+      <c r="H9" s="13">
+        <v>0.78888879999999995</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>20</v>
-      </c>
+      <c r="A10" s="4"/>
       <c r="B10" s="5" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" t="s">
-        <v>19</v>
+        <v>16</v>
+      </c>
+      <c r="E10" t="s">
+        <v>17</v>
       </c>
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
       <c r="H10" s="13">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="5"/>
+      <c r="A11" s="4"/>
+      <c r="B11" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="C11" s="5"/>
-      <c r="D11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" t="s">
-        <v>31</v>
-      </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6">
-        <v>6.4820000000000002</v>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="14" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="5"/>
+        <v>20</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="C12" s="5"/>
       <c r="D12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" t="s">
         <v>13</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E13" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6">
+        <v>6.4820000000000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6">
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6">
         <f>0.96035*2</f>
         <v>1.9207000000000001</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F15" s="6"/>
@@ -2799,52 +3060,62 @@
       <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="11"/>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="11"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="11"/>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="11"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="11"/>
-      <c r="H20" s="12"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="11"/>
-      <c r="H21" s="12"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="11"/>
+      <c r="H22" s="12"/>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="11"/>
+      <c r="H23" s="12"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A20:A21">
+  <conditionalFormatting sqref="A22:A23">
     <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:B4 A16:B19">
+  <conditionalFormatting sqref="A4:B4 A18:B21">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A6:B10">
+  <conditionalFormatting sqref="A8:B12">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E6:E10">
+  <conditionalFormatting sqref="E8:E12">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
